--- a/data/trans_orig/cron_index-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad total</t>
+          <t>Índice de cronicidad total (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,54</t>
+          <t>0,34; 0,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,72</t>
+          <t>0,43; 0,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,71</t>
+          <t>0,47; 0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,05</t>
+          <t>0,73; 1,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,64</t>
+          <t>0,43; 0,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,87</t>
+          <t>0,6; 0,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,82</t>
+          <t>0,51; 0,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,92</t>
+          <t>0,7; 0,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,57</t>
+          <t>0,41; 0,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,74</t>
+          <t>0,54; 0,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,7</t>
+          <t>0,52; 0,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 0,95</t>
+          <t>0,75; 0,94</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,76</t>
+          <t>0,51; 0,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,7</t>
+          <t>0,5; 0,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,98</t>
+          <t>0,71; 0,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,91</t>
+          <t>0,7; 0,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,96</t>
+          <t>0,74; 0,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,98</t>
+          <t>0,75; 0,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,69</t>
+          <t>0,56; 0,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,58</t>
+          <t>0,38; 0,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,52 +1006,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,67</t>
+          <t>0,46; 0,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,16</t>
+          <t>0,85; 1,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,84</t>
+          <t>0,62; 0,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,05</t>
+          <t>0,76; 1,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,79</t>
+          <t>0,56; 0,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,26</t>
+          <t>0,99; 1,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,68</t>
+          <t>0,53; 0,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,91</t>
+          <t>0,72; 0,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,69</t>
+          <t>0,53; 0,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,18</t>
+          <t>0,95; 1,18</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,59</t>
+          <t>0,4; 0,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,74</t>
+          <t>0,52; 0,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,87</t>
+          <t>0,62; 0,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,14</t>
+          <t>0,78; 1,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,78</t>
+          <t>0,58; 0,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,17 +1166,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,98</t>
+          <t>0,75; 0,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,46</t>
+          <t>0,86; 1,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,65</t>
+          <t>0,51; 0,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,89</t>
+          <t>0,71; 0,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,67</t>
+          <t>0,39; 0,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,52 +1286,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,7</t>
+          <t>0,42; 0,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,15</t>
+          <t>0,81; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,01</t>
+          <t>0,64; 1,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,34</t>
+          <t>0,93; 1,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,97</t>
+          <t>0,65; 0,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,37</t>
+          <t>0,61; 1,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,8</t>
+          <t>0,56; 0,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,07</t>
+          <t>0,8; 1,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,79</t>
+          <t>0,58; 0,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,2</t>
+          <t>0,73; 1,21</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,59</t>
+          <t>0,39; 0,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1426,52 +1426,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,68</t>
+          <t>0,44; 0,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,47</t>
+          <t>1,14; 1,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,83</t>
+          <t>0,57; 0,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,13</t>
+          <t>0,82; 1,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,88</t>
+          <t>0,62; 0,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,42</t>
+          <t>1,1; 1,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,66</t>
+          <t>0,52; 0,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 0,99</t>
+          <t>0,78; 0,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,75</t>
+          <t>0,55; 0,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,4</t>
+          <t>1,17; 1,4</t>
         </is>
       </c>
     </row>
@@ -1566,17 +1566,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,74</t>
+          <t>0,54; 0,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,07</t>
+          <t>0,83; 1,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,77</t>
+          <t>0,6; 0,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,78</t>
+          <t>0,58; 0,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,2</t>
+          <t>1,06; 2,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,66</t>
+          <t>0,53; 0,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,79</t>
+          <t>0,67; 0,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,73</t>
+          <t>0,59; 0,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,99</t>
+          <t>1,0; 1,9</t>
         </is>
       </c>
     </row>
@@ -1696,42 +1696,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,71</t>
+          <t>0,56; 0,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,59</t>
+          <t>0,44; 0,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0,57; 0,73</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0,25; 0,78</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,69; 0,86</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,56; 0,72</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0,24; 0,79</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 0,87</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,55; 0,72</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,89</t>
+          <t>0,71; 0,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,01</t>
+          <t>0,82; 1,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,63</t>
+          <t>0,52; 0,64</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,54</t>
+          <t>0,48; 0,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,67</t>
+          <t>0,58; 0,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,46</t>
+          <t>1,0; 1,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,19</t>
+          <t>0,9; 1,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_index-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,55</t>
+          <t>0,33; 0,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,69</t>
+          <t>0,46; 0,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,7</t>
+          <t>0,46; 0,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,04</t>
+          <t>0,74; 1,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,66</t>
+          <t>0,41; 0,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,88</t>
+          <t>0,59; 0,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,79</t>
+          <t>0,52; 0,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,93</t>
+          <t>0,68; 0,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,73</t>
+          <t>0,56; 0,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,71</t>
+          <t>0,53; 0,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,94</t>
+          <t>0,74; 0,92</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,22 +856,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,54</t>
+          <t>0,37; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,74</t>
+          <t>0,5; 0,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,69</t>
+          <t>0,5; 0,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,98</t>
+          <t>0,71; 0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,22 +881,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,97</t>
+          <t>0,74; 0,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,96</t>
+          <t>0,74; 0,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 0,97</t>
+          <t>0,77; 0,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,7</t>
+          <t>0,56; 0,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,8</t>
+          <t>0,65; 0,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 0,94</t>
+          <t>0,77; 0,93</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,57</t>
+          <t>0,37; 0,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,86</t>
+          <t>0,59; 0,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,67</t>
+          <t>0,47; 0,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,17</t>
+          <t>0,85; 1,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,84</t>
+          <t>0,6; 0,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,06</t>
+          <t>0,77; 1,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,79</t>
+          <t>0,56; 0,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,27</t>
+          <t>0,97; 1,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,68</t>
+          <t>0,52; 0,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,92</t>
+          <t>0,71; 0,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,69</t>
+          <t>0,54; 0,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,18</t>
+          <t>0,95; 1,17</t>
         </is>
       </c>
     </row>
@@ -1083,47 +1083,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,67</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,87</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>0,95</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,58</t>
+          <t>0,4; 0,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,87</t>
+          <t>0,63; 0,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,13</t>
+          <t>0,74; 1,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,22 +1161,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,04</t>
+          <t>0,76; 1,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,99</t>
+          <t>0,75; 1,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,46</t>
+          <t>0,89; 1,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,64</t>
+          <t>0,51; 0,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,89</t>
+          <t>0,72; 0,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,3</t>
+          <t>0,86; 1,06</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,09</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,66</t>
+          <t>0,4; 0,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,96</t>
+          <t>0,56; 0,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,27 +1291,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,16</t>
+          <t>0,74; 1,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,03</t>
+          <t>0,64; 1,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,37</t>
+          <t>0,94; 1,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,99</t>
+          <t>0,63; 0,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,37</t>
+          <t>1,1; 1,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,1</t>
+          <t>0,79; 1,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,81</t>
+          <t>0,56; 0,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,21</t>
+          <t>0,98; 1,21</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,6</t>
+          <t>0,39; 0,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,95</t>
+          <t>0,66; 0,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,69</t>
+          <t>0,46; 0,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,82</t>
+          <t>0,58; 0,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,88</t>
+          <t>0,6; 0,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,41</t>
+          <t>1,1; 1,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,67</t>
+          <t>0,51; 0,67</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,99</t>
+          <t>0,77; 0,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,4</t>
+          <t>1,16; 1,39</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,06</t>
         </is>
       </c>
     </row>
@@ -1561,22 +1561,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,75</t>
+          <t>0,55; 0,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,73</t>
+          <t>0,54; 0,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,08</t>
+          <t>0,87; 1,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,78</t>
+          <t>0,6; 0,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,79</t>
+          <t>0,58; 0,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,29</t>
+          <t>1,02; 1,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,74</t>
+          <t>0,6; 0,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,9</t>
+          <t>0,98; 1,13</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,81</t>
         </is>
       </c>
     </row>
@@ -1696,42 +1696,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0,55; 0,72</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0,44; 0,59</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0,57; 0,72</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0,64; 0,82</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,69; 0,86</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,56; 0,72</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 0,58</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 0,73</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0,25; 0,78</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 0,86</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 0,72</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,88</t>
+          <t>0,7; 0,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,0</t>
+          <t>0,81; 0,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,64</t>
+          <t>0,52; 0,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,86</t>
+          <t>0,75; 0,88</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,54</t>
+          <t>0,47; 0,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,66</t>
+          <t>0,58; 0,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,94</t>
+          <t>0,86; 0,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,8</t>
+          <t>0,71; 0,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,45</t>
+          <t>0,97; 1,05</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,17</t>
+          <t>0,93; 0,99</t>
         </is>
       </c>
     </row>
